--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -567,6 +567,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -581,6 +585,10 @@
                      </t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -650,7 +658,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -672,7 +682,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -694,7 +706,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -716,7 +730,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -738,7 +754,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -760,7 +778,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -782,7 +802,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -804,7 +826,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -826,7 +850,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -848,7 +874,9 @@
       <c r="C25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -870,7 +898,9 @@
       <c r="C26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -892,7 +922,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -914,7 +946,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -936,7 +970,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -958,7 +994,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -980,7 +1018,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -1002,7 +1042,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1024,7 +1066,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1046,7 +1090,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1068,7 +1114,9 @@
       <c r="C35" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1090,7 +1138,9 @@
       <c r="C36" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1112,7 +1162,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1134,7 +1186,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>3</v>
       </c>
@@ -1280,6 +1334,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1292,6 +1350,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1362,7 +1424,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -1384,7 +1448,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -1406,7 +1472,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1428,7 +1496,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -1450,7 +1520,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1472,7 +1544,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -1494,7 +1568,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -1516,7 +1592,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -1538,7 +1616,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
@@ -1684,6 +1764,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1699,6 +1783,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1768,7 +1856,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
       </c>
@@ -1790,7 +1880,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -1812,7 +1904,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -1835,7 +1929,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -1858,7 +1954,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1881,7 +1979,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1903,7 +2003,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>3</v>
       </c>
@@ -1925,7 +2027,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2071,6 +2175,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2086,6 +2194,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2155,7 +2267,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2177,7 +2291,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2199,7 +2315,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2221,7 +2339,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2243,7 +2363,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -2265,7 +2387,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2287,7 +2411,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -2309,7 +2435,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2331,7 +2459,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -2353,7 +2483,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2375,7 +2507,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -2397,7 +2531,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -2419,7 +2555,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -2441,7 +2579,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2463,7 +2603,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -2485,7 +2627,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -2507,7 +2651,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -2529,7 +2675,9 @@
       <c r="C33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>7</v>
       </c>
@@ -2551,7 +2699,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -2697,6 +2847,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2711,6 +2865,10 @@
                      </t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2780,7 +2938,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2802,7 +2962,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2824,7 +2986,9 @@
       <c r="C18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -2846,7 +3010,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -2868,7 +3034,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -2890,7 +3058,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2912,7 +3082,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2934,7 +3106,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2956,7 +3130,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2978,7 +3154,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -3000,7 +3178,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -3022,7 +3202,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -3044,7 +3226,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -3066,7 +3250,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -3088,7 +3274,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -3110,7 +3298,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -3132,7 +3322,9 @@
       <c r="C32" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -3154,7 +3346,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -3176,7 +3370,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -3322,6 +3518,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3337,6 +3537,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3406,7 +3610,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>7</v>
       </c>
@@ -3428,7 +3634,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -3450,7 +3658,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -3473,7 +3683,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -3496,7 +3708,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3519,7 +3733,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3541,7 +3757,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>3</v>
       </c>
@@ -3563,7 +3781,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -3709,6 +3929,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3723,6 +3947,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3792,7 +4020,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3814,7 +4044,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3836,7 +4068,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3858,7 +4092,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -3880,7 +4116,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -3902,7 +4140,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -3924,7 +4164,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -3946,7 +4188,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -3968,7 +4212,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -3990,7 +4236,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -4012,7 +4260,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -4034,7 +4284,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -4056,7 +4308,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -4078,7 +4332,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -4100,7 +4356,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -4122,7 +4380,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -4144,7 +4404,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -4166,7 +4428,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>8</v>
       </c>
@@ -4188,7 +4452,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -4210,7 +4476,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>6</v>
       </c>
@@ -4232,7 +4500,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -4254,7 +4524,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -4276,7 +4548,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -4422,6 +4696,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4436,6 +4714,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4505,7 +4787,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4527,7 +4811,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4549,7 +4835,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4571,7 +4859,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -4593,7 +4883,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -4615,7 +4907,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -4637,7 +4931,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -4659,7 +4955,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -4681,7 +4979,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -4703,7 +5003,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -4725,7 +5027,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -4747,7 +5051,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -4769,7 +5075,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -4791,7 +5099,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -4813,7 +5123,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -4835,7 +5147,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -4857,7 +5171,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -4879,7 +5195,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>7</v>
       </c>
@@ -5025,6 +5343,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5039,6 +5361,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5108,7 +5434,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5130,7 +5458,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5152,7 +5482,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -5174,7 +5506,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -5196,7 +5530,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -5218,7 +5554,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -5240,7 +5578,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -5262,7 +5602,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -5284,7 +5626,9 @@
       <c r="C24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -5306,7 +5650,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -5328,7 +5674,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -5350,7 +5698,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -5372,7 +5722,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -5394,7 +5746,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -5416,7 +5770,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -5438,7 +5794,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -5460,7 +5818,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -5482,7 +5842,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -5504,7 +5866,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -5526,7 +5890,9 @@
       <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>8</v>
       </c>
@@ -5548,7 +5914,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -5570,7 +5938,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -5592,7 +5962,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -5738,6 +6110,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5753,6 +6129,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5822,7 +6202,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5844,7 +6226,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5866,7 +6250,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -5888,7 +6274,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -5910,7 +6298,9 @@
       <c r="C20" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -5932,7 +6322,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -5954,7 +6346,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -5976,7 +6370,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -5998,7 +6394,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -6020,7 +6418,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -6042,7 +6442,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -6188,6 +6590,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6202,6 +6608,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6271,7 +6681,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -6293,7 +6705,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -6315,7 +6729,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -6337,7 +6753,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -6359,7 +6777,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -6381,7 +6801,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -6403,7 +6825,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -6425,7 +6849,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -6447,7 +6873,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -6469,7 +6897,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -6491,7 +6921,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -6513,7 +6945,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -6535,7 +6969,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -6557,7 +6993,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -6579,7 +7017,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -6601,7 +7041,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -6623,7 +7065,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -6645,7 +7089,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -6667,7 +7113,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -6689,7 +7137,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -6711,7 +7161,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -6733,7 +7185,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -6755,7 +7209,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -6901,6 +7357,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6914,6 +7374,10 @@
 Workshop/Lab	: 800-1000 sft </t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6983,7 +7447,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -7005,7 +7471,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -7027,7 +7495,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -7049,7 +7519,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -7071,7 +7543,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -7093,7 +7567,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -7115,7 +7591,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -7137,7 +7615,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -7159,7 +7639,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -7181,7 +7663,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -7203,7 +7687,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -7225,7 +7711,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -7247,7 +7735,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -7269,7 +7759,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -7291,7 +7783,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -7313,7 +7807,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -7335,7 +7831,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -7357,7 +7855,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -3182,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Weighing Scale (Preferred capacity mm)</t>
+          <t>Weighing Scale (Preferred capacity 10 kg)</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -143,6 +143,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6051,7 +6057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -6110,10 +6116,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6129,10 +6131,6 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6191,12 +6189,12 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computers/Laptop</t>
+          <t>Computer/ Laptop</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -6215,12 +6213,12 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Projector &amp; Screen (HD quality, HDMI support, 3000+ lumens)</t>
+          <t>Multimedia Projector</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -6230,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -6239,22 +6237,22 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Table for Printing</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -6263,12 +6261,12 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Mannequins/Dress Forms (Female and male standard sizes)</t>
+          <t>Fabric Cutting Table</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -6278,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -6287,16 +6285,16 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Single needle lock stitch machine</t>
+          <t>Pattern Making Table</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -6311,22 +6309,22 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Overlock machine</t>
+          <t>Mannequin doll (Child, male and female)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -6335,22 +6333,22 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Cutting table (60”x 50”)</t>
+          <t>Sample Fashion Garments Product</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -6359,22 +6357,22 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Electric iron</t>
+          <t>Sample Technical Package</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -6383,22 +6381,22 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Electric steam iron with iron table</t>
+          <t>Sample Motif and Embellishment</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -6407,12 +6405,12 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Scissors (10”-12”)</t>
+          <t>Sets of Pattern Making Curves</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
@@ -6422,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -6431,12 +6429,12 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Sewing tool box</t>
+          <t>Tracing Wheels</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -6446,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -6454,57 +6452,321 @@
       </c>
       <c r="G26" s="9" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Hoops and Frames Set</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Embroidery Machine</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Different Dices for Block for Printing</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Different Screen for Printing</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Burner for Dyeing and Printing</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Fabric Cutting Scissor (6-10 inches)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Straight Knife</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Single Needle Machine (Domestic)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="14.15" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Single Needle Machine (Industrial)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="9">
+        <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Overlock Machines</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9">
+        <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="14.15" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Industrial Iron with Table</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" s="9">
+        <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="10">
-        <f>SUM(E16:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>SUM(F16:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="13" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="15">
+        <f>SUM(E16:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="15">
+        <f>SUM(F16:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
-        <f>F27/E27*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="9.75" customHeight="1"/>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="15">
+        <f>F38/E38*100</f>
+        <v/>
+      </c>
+      <c r="G39" s="13" t="n"/>
+    </row>
+    <row r="40" ht="9.75" customHeight="1"/>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
-        <f>F28*30/100</f>
-        <v/>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="15">
+        <f>F39*30/100</f>
+        <v/>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6512,13 +6774,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/lab-standards/PKSF-lab-standard.xlsx
+++ b/lab-standards/PKSF-lab-standard.xlsx
@@ -653,7 +653,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -677,7 +677,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -701,7 +701,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -725,7 +725,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -749,7 +749,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -773,7 +773,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -797,7 +797,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -821,7 +821,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -845,7 +845,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -893,7 +893,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -917,7 +917,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -941,7 +941,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -989,7 +989,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1061,7 +1061,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -1085,7 +1085,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1109,7 +1109,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1133,7 +1133,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1157,7 +1157,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1181,7 +1181,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1205,7 +1205,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1213,18 +1213,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1233,7 +1233,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1250,11 +1250,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1418,7 +1418,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -1491,7 +1491,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -1515,7 +1515,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -1539,7 +1539,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1587,7 +1587,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -1635,7 +1635,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1643,18 +1643,18 @@
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
+      <c r="E25" s="15">
         <f>SUM(E16:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>SUM(F16:F24)</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1663,7 +1663,7 @@
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
+      <c r="F26" s="15">
         <f>F25/E25*100</f>
         <v/>
       </c>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="27" ht="9.75" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1680,11 +1680,11 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F26*30/100</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1851,7 +1851,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1866,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -1875,7 +1875,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -1899,7 +1899,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -1923,7 +1923,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1948,7 +1948,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -1973,7 +1973,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1998,7 +1998,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -2022,7 +2022,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2046,7 +2046,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2054,18 +2054,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="15">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="15">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2074,7 +2074,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2091,11 +2091,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2262,7 +2262,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2286,7 +2286,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2310,7 +2310,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -2334,7 +2334,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2358,7 +2358,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2406,7 +2406,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -2430,7 +2430,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -2454,7 +2454,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -2478,7 +2478,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2502,7 +2502,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -2526,7 +2526,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2574,7 +2574,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -2598,7 +2598,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2622,7 +2622,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2646,7 +2646,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -2670,7 +2670,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -2694,7 +2694,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -2718,7 +2718,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2726,18 +2726,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2746,7 +2746,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2763,11 +2763,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2933,7 +2933,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2957,7 +2957,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2981,7 +2981,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3005,7 +3005,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3029,7 +3029,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3053,7 +3053,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3077,7 +3077,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3101,7 +3101,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3125,7 +3125,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3149,7 +3149,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3173,7 +3173,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3197,7 +3197,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3221,7 +3221,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3245,7 +3245,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3269,7 +3269,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3293,7 +3293,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3317,7 +3317,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3341,7 +3341,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3365,7 +3365,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3389,7 +3389,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3397,18 +3397,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3417,7 +3417,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3434,11 +3434,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3605,7 +3605,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -3629,7 +3629,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -3653,7 +3653,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -3677,7 +3677,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3702,7 +3702,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3718,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -3727,7 +3727,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3752,7 +3752,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3776,7 +3776,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3800,7 +3800,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3808,18 +3808,18 @@
       <c r="B24" s="11" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="15">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="15">
         <f>SUM(F16:F23)</f>
         <v/>
       </c>
       <c r="G24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3828,7 +3828,7 @@
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>F24/E24*100</f>
         <v/>
       </c>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="26" ht="9.75" customHeight="1"/>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3845,11 +3845,11 @@
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10">
+      <c r="F27" s="15">
         <f>F25*30/100</f>
         <v/>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4015,7 +4015,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4039,7 +4039,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4063,7 +4063,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4087,7 +4087,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4111,7 +4111,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -4159,7 +4159,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4183,7 +4183,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4207,7 +4207,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -4231,7 +4231,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -4255,7 +4255,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -4279,7 +4279,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -4303,7 +4303,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -4327,7 +4327,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -4351,7 +4351,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -4375,7 +4375,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -4390,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -4399,7 +4399,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -4423,7 +4423,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4447,7 +4447,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -4471,7 +4471,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4486,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -4495,7 +4495,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -4510,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -4519,7 +4519,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4543,7 +4543,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4567,7 +4567,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -4575,18 +4575,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -4595,7 +4595,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -4612,11 +4612,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4782,7 +4782,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -4806,7 +4806,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4830,7 +4830,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4854,7 +4854,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -4878,7 +4878,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -4902,7 +4902,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -4926,7 +4926,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -4950,7 +4950,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -4974,7 +4974,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -4998,7 +4998,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -5022,7 +5022,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5046,7 +5046,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5070,7 +5070,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5094,7 +5094,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5118,7 +5118,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -5142,7 +5142,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5157,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -5166,7 +5166,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -5190,7 +5190,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -5214,7 +5214,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5222,18 +5222,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -5242,7 +5242,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -5250,7 +5250,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -5259,11 +5259,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -5429,7 +5429,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -5453,7 +5453,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -5477,7 +5477,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -5501,7 +5501,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -5549,7 +5549,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -5573,7 +5573,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -5597,7 +5597,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -5621,7 +5621,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -5645,7 +5645,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -5669,7 +5669,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -5693,7 +5693,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -5708,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -5717,7 +5717,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -5732,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -5741,7 +5741,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -5765,7 +5765,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -5789,7 +5789,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -5813,7 +5813,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -5837,7 +5837,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -5861,7 +5861,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -5876,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -5885,7 +5885,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -5909,7 +5909,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
@@ -5933,7 +5933,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -5981,7 +5981,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -5989,18 +5989,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -6009,7 +6009,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -6026,11 +6026,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6116,6 +6116,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6131,6 +6135,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6932,7 +6940,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -6956,7 +6964,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -6980,7 +6988,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7004,7 +7012,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7019,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -7028,7 +7036,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7043,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -7052,7 +7060,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7076,7 +7084,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7100,7 +7108,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7115,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -7124,7 +7132,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7148,7 +7156,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7172,7 +7180,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7196,7 +7204,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7211,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -7220,7 +7228,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -7244,7 +7252,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7268,7 +7276,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -7283,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -7292,7 +7300,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -7316,7 +7324,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -7331,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -7340,7 +7348,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -7364,7 +7372,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -7388,7 +7396,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="14" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7403,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
@@ -7412,7 +7420,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="14" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -7436,7 +7444,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="14" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -7451,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -7460,7 +7468,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="14" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -7484,7 +7492,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -7492,18 +7500,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="15">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="15">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -7512,7 +7520,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10">
+      <c r="F40" s="15">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -7520,7 +7528,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -7529,11 +7537,11 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="10">
+      <c r="F42" s="15">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -7698,7 +7706,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -7713,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -7722,7 +7730,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -7737,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -7746,7 +7754,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -7761,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -7770,7 +7778,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -7794,7 +7802,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -7809,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -7818,7 +7826,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -7833,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -7842,7 +7850,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -7857,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -7866,7 +7874,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -7881,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -7890,7 +7898,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -7905,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -7914,7 +7922,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7929,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -7938,7 +7946,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -7953,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -7962,7 +7970,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7977,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -7986,7 +7994,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -8010,7 +8018,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -8034,7 +8042,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -8058,7 +8066,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -8082,7 +8090,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -8097,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -8106,7 +8114,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -8130,7 +8138,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -8138,18 +8146,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -8158,7 +8166,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -8166,7 +8174,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -8175,11 +8183,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
